--- a/Data/EXCEL/Transfer/salemon/202208/9928-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/9928-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7400E8A5-FB15-46A5-B219-70441116A03B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AACBD72-DC45-464D-BA76-0AE5A37178FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="9928-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1219,22 +1227,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q288"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.875" customWidth="1"/>
-    <col min="2" max="6" width="10.125" customWidth="1"/>
-    <col min="7" max="7" width="11.75" customWidth="1"/>
-    <col min="8" max="9" width="10.125" customWidth="1"/>
-    <col min="10" max="10" width="9.5" customWidth="1"/>
-    <col min="11" max="11" width="10.125" customWidth="1"/>
-    <col min="12" max="12" width="9.5" customWidth="1"/>
-    <col min="13" max="14" width="10.125" customWidth="1"/>
-    <col min="15" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="10.125" customWidth="1"/>
-    <col min="17" max="17" width="10.625" customWidth="1"/>
+    <col min="1" max="1" width="16.875" customWidth="1"/>
+    <col min="2" max="6" width="14.125" customWidth="1"/>
+    <col min="7" max="7" width="16.125" customWidth="1"/>
+    <col min="8" max="9" width="14.125" customWidth="1"/>
+    <col min="10" max="10" width="13.5" customWidth="1"/>
+    <col min="11" max="11" width="14.125" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="13" max="14" width="14.125" customWidth="1"/>
+    <col min="15" max="15" width="13.5" customWidth="1"/>
+    <col min="16" max="17" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1261,7 +1268,7 @@
       <c r="P1" s="15"/>
       <c r="Q1" s="16"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="12"/>
       <c r="B2" s="11" t="s">
         <v>4</v>
@@ -1300,7 +1307,7 @@
       </c>
       <c r="Q2" s="16"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1343,7 +1350,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -1382,7 +1389,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44774</v>
       </c>
@@ -1435,7 +1442,7 @@
         <v>8.93</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44743</v>
       </c>
@@ -1488,7 +1495,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44713</v>
       </c>
@@ -1541,7 +1548,7 @@
         <v>9.7100000000000009</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44682</v>
       </c>
@@ -1594,7 +1601,7 @@
         <v>6.62</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44652</v>
       </c>
@@ -1647,7 +1654,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44621</v>
       </c>
@@ -1700,7 +1707,7 @@
         <v>7.12</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44593</v>
       </c>
@@ -1753,7 +1760,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44562</v>
       </c>
@@ -1806,7 +1813,7 @@
         <v>7.78</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44531</v>
       </c>
@@ -1859,7 +1866,7 @@
         <v>6.22</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44501</v>
       </c>
@@ -1912,7 +1919,7 @@
         <v>4.09</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44470</v>
       </c>
@@ -1965,7 +1972,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44440</v>
       </c>
@@ -2018,7 +2025,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44409</v>
       </c>
@@ -2071,7 +2078,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44378</v>
       </c>
@@ -2124,7 +2131,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44348</v>
       </c>
@@ -2177,7 +2184,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44317</v>
       </c>
@@ -2230,7 +2237,7 @@
         <v>5.87</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44287</v>
       </c>
@@ -2283,7 +2290,7 @@
         <v>9.15</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44256</v>
       </c>
@@ -2336,7 +2343,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44228</v>
       </c>
@@ -2389,7 +2396,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44197</v>
       </c>
@@ -2442,7 +2449,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44166</v>
       </c>
@@ -2495,7 +2502,7 @@
         <v>4.41</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44136</v>
       </c>
@@ -2548,7 +2555,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44105</v>
       </c>
@@ -2601,7 +2608,7 @@
         <v>6.21</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44075</v>
       </c>
@@ -2654,7 +2661,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44044</v>
       </c>
@@ -2707,7 +2714,7 @@
         <v>5.59</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>44013</v>
       </c>
@@ -2760,7 +2767,7 @@
         <v>9.02</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43983</v>
       </c>
@@ -2813,7 +2820,7 @@
         <v>8.24</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43952</v>
       </c>
@@ -2866,7 +2873,7 @@
         <v>7.79</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43922</v>
       </c>
@@ -2919,7 +2926,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43891</v>
       </c>
@@ -2972,7 +2979,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43862</v>
       </c>
@@ -3025,7 +3032,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43831</v>
       </c>
@@ -3078,7 +3085,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43800</v>
       </c>
@@ -3131,7 +3138,7 @@
         <v>-3.84</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43770</v>
       </c>
@@ -3184,7 +3191,7 @@
         <v>-5.84</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43739</v>
       </c>
@@ -3237,7 +3244,7 @@
         <v>-2.65</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43709</v>
       </c>
@@ -3290,7 +3297,7 @@
         <v>-4.68</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43678</v>
       </c>
@@ -3343,7 +3350,7 @@
         <v>-2.97</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43647</v>
       </c>
@@ -3396,7 +3403,7 @@
         <v>-7.89</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43617</v>
       </c>
@@ -3449,7 +3456,7 @@
         <v>-7.3</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43586</v>
       </c>
@@ -3502,7 +3509,7 @@
         <v>-5.91</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43556</v>
       </c>
@@ -3555,7 +3562,7 @@
         <v>-5.33</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43525</v>
       </c>
@@ -3608,7 +3615,7 @@
         <v>-10.8</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43497</v>
       </c>
@@ -3661,7 +3668,7 @@
         <v>-10.4</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43466</v>
       </c>
@@ -3714,7 +3721,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43435</v>
       </c>
@@ -3767,7 +3774,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43405</v>
       </c>
@@ -3820,7 +3827,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43374</v>
       </c>
@@ -3873,7 +3880,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43344</v>
       </c>
@@ -3926,7 +3933,7 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43313</v>
       </c>
@@ -3979,7 +3986,7 @@
         <v>-1.1399999999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43282</v>
       </c>
@@ -4032,7 +4039,7 @@
         <v>-0.62</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43252</v>
       </c>
@@ -4085,7 +4092,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43221</v>
       </c>
@@ -4138,7 +4145,7 @@
         <v>-2.44</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43191</v>
       </c>
@@ -4191,7 +4198,7 @@
         <v>-0.89</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43160</v>
       </c>
@@ -4244,7 +4251,7 @@
         <v>-2.31</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>43132</v>
       </c>
@@ -4297,7 +4304,7 @@
         <v>-0.51</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>43101</v>
       </c>
@@ -4350,7 +4357,7 @@
         <v>-29.2</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>43070</v>
       </c>
@@ -4403,7 +4410,7 @@
         <v>-5.87</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>43040</v>
       </c>
@@ -4456,7 +4463,7 @@
         <v>-6.52</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>43009</v>
       </c>
@@ -4509,7 +4516,7 @@
         <v>-6.74</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="5" customFormat="1">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>42979</v>
       </c>
@@ -4562,7 +4569,7 @@
         <v>-3.97</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="5" customFormat="1">
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>42948</v>
       </c>
@@ -4615,7 +4622,7 @@
         <v>-3.66</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="5" customFormat="1">
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>42917</v>
       </c>
@@ -4668,7 +4675,7 @@
         <v>-3.68</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="5" customFormat="1">
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>42887</v>
       </c>
@@ -4721,7 +4728,7 @@
         <v>-7.07</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>42856</v>
       </c>
@@ -4774,7 +4781,7 @@
         <v>-8.32</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>42826</v>
       </c>
@@ -4827,7 +4834,7 @@
         <v>-10.9</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="5" customFormat="1">
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>42795</v>
       </c>
@@ -4880,7 +4887,7 @@
         <v>-8.89</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="5" customFormat="1">
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>42767</v>
       </c>
@@ -4933,7 +4940,7 @@
         <v>-15.2</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="5" customFormat="1">
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>42736</v>
       </c>
@@ -4986,7 +4993,7 @@
         <v>-5.1100000000000003</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="5" customFormat="1">
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>42705</v>
       </c>
@@ -5039,7 +5046,7 @@
         <v>-17.8</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="5" customFormat="1">
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>42675</v>
       </c>
@@ -5092,7 +5099,7 @@
         <v>-15.7</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="5" customFormat="1">
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>42644</v>
       </c>
@@ -5145,7 +5152,7 @@
         <v>-12.9</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="5" customFormat="1">
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>42614</v>
       </c>
@@ -5198,7 +5205,7 @@
         <v>-10.8</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="5" customFormat="1">
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>42583</v>
       </c>
@@ -5251,7 +5258,7 @@
         <v>-7.32</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="5" customFormat="1">
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>42552</v>
       </c>
@@ -5304,7 +5311,7 @@
         <v>-6.13</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="5" customFormat="1">
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>42522</v>
       </c>
@@ -5357,7 +5364,7 @@
         <v>-0.39</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="5" customFormat="1">
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>42491</v>
       </c>
@@ -5410,7 +5417,7 @@
         <v>7.49</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="5" customFormat="1">
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>42461</v>
       </c>
@@ -5463,7 +5470,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="5" customFormat="1">
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>42430</v>
       </c>
@@ -5516,7 +5523,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="5" customFormat="1">
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>42401</v>
       </c>
@@ -5569,7 +5576,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="5" customFormat="1">
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>42370</v>
       </c>
@@ -5622,7 +5629,7 @@
         <v>43.1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="5" customFormat="1">
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>42339</v>
       </c>
@@ -5675,7 +5682,7 @@
         <v>-6.3</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="5" customFormat="1">
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>42309</v>
       </c>
@@ -5728,7 +5735,7 @@
         <v>-3.53</v>
       </c>
     </row>
-    <row r="87" spans="1:17" s="5" customFormat="1">
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>42278</v>
       </c>
@@ -5781,7 +5788,7 @@
         <v>-9.07</v>
       </c>
     </row>
-    <row r="88" spans="1:17" s="5" customFormat="1">
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>42248</v>
       </c>
@@ -5834,7 +5841,7 @@
         <v>-8.32</v>
       </c>
     </row>
-    <row r="89" spans="1:17" s="5" customFormat="1">
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>42217</v>
       </c>
@@ -5887,7 +5894,7 @@
         <v>-11.3</v>
       </c>
     </row>
-    <row r="90" spans="1:17" s="5" customFormat="1">
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>42186</v>
       </c>
@@ -5940,7 +5947,7 @@
         <v>-12.6</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="5" customFormat="1">
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>42156</v>
       </c>
@@ -5993,7 +6000,7 @@
         <v>-17.2</v>
       </c>
     </row>
-    <row r="92" spans="1:17" s="5" customFormat="1">
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>42125</v>
       </c>
@@ -6046,7 +6053,7 @@
         <v>-20.7</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="5" customFormat="1">
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>42095</v>
       </c>
@@ -6099,7 +6106,7 @@
         <v>-25.9</v>
       </c>
     </row>
-    <row r="94" spans="1:17" s="5" customFormat="1">
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>42064</v>
       </c>
@@ -6152,7 +6159,7 @@
         <v>-32</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="5" customFormat="1">
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>42036</v>
       </c>
@@ -6205,7 +6212,7 @@
         <v>-28.2</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="5" customFormat="1">
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>42005</v>
       </c>
@@ -6258,7 +6265,7 @@
         <v>-36.9</v>
       </c>
     </row>
-    <row r="97" spans="1:17" s="5" customFormat="1">
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>41974</v>
       </c>
@@ -6311,7 +6318,7 @@
         <v>-19.5</v>
       </c>
     </row>
-    <row r="98" spans="1:17" s="5" customFormat="1">
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>41944</v>
       </c>
@@ -6364,7 +6371,7 @@
         <v>-17.8</v>
       </c>
     </row>
-    <row r="99" spans="1:17" s="5" customFormat="1">
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>41913</v>
       </c>
@@ -6417,7 +6424,7 @@
         <v>-15.2</v>
       </c>
     </row>
-    <row r="100" spans="1:17" s="5" customFormat="1">
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>41883</v>
       </c>
@@ -6470,7 +6477,7 @@
         <v>-18.600000000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="5" customFormat="1">
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>41852</v>
       </c>
@@ -6523,7 +6530,7 @@
         <v>-14.7</v>
       </c>
     </row>
-    <row r="102" spans="1:17" s="5" customFormat="1">
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>41821</v>
       </c>
@@ -6576,7 +6583,7 @@
         <v>-13.9</v>
       </c>
     </row>
-    <row r="103" spans="1:17" s="5" customFormat="1">
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>41791</v>
       </c>
@@ -6629,7 +6636,7 @@
         <v>-11.5</v>
       </c>
     </row>
-    <row r="104" spans="1:17" s="5" customFormat="1">
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>41760</v>
       </c>
@@ -6682,7 +6689,7 @@
         <v>-10.1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" s="5" customFormat="1">
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>41730</v>
       </c>
@@ -6735,7 +6742,7 @@
         <v>-9.74</v>
       </c>
     </row>
-    <row r="106" spans="1:17" s="5" customFormat="1">
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>41699</v>
       </c>
@@ -6788,7 +6795,7 @@
         <v>-6.65</v>
       </c>
     </row>
-    <row r="107" spans="1:17" s="5" customFormat="1">
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>41671</v>
       </c>
@@ -6841,7 +6848,7 @@
         <v>-5.93</v>
       </c>
     </row>
-    <row r="108" spans="1:17" s="5" customFormat="1">
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>41640</v>
       </c>
@@ -6894,7 +6901,7 @@
         <v>-5.43</v>
       </c>
     </row>
-    <row r="109" spans="1:17" s="5" customFormat="1">
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>41609</v>
       </c>
@@ -6947,7 +6954,7 @@
         <v>-5.53</v>
       </c>
     </row>
-    <row r="110" spans="1:17" s="5" customFormat="1">
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>41579</v>
       </c>
@@ -7000,7 +7007,7 @@
         <v>-7.03</v>
       </c>
     </row>
-    <row r="111" spans="1:17" s="5" customFormat="1">
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>41548</v>
       </c>
@@ -7053,7 +7060,7 @@
         <v>-9.19</v>
       </c>
     </row>
-    <row r="112" spans="1:17" s="5" customFormat="1">
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>41518</v>
       </c>
@@ -7106,7 +7113,7 @@
         <v>-12.2</v>
       </c>
     </row>
-    <row r="113" spans="1:17" s="5" customFormat="1">
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>41487</v>
       </c>
@@ -7159,7 +7166,7 @@
         <v>-13.7</v>
       </c>
     </row>
-    <row r="114" spans="1:17" s="5" customFormat="1">
+    <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>41456</v>
       </c>
@@ -7212,7 +7219,7 @@
         <v>-9.7799999999999994</v>
       </c>
     </row>
-    <row r="115" spans="1:17" s="5" customFormat="1">
+    <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>41426</v>
       </c>
@@ -7265,7 +7272,7 @@
         <v>-9.9499999999999993</v>
       </c>
     </row>
-    <row r="116" spans="1:17" s="5" customFormat="1">
+    <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>41395</v>
       </c>
@@ -7318,7 +7325,7 @@
         <v>-11.4</v>
       </c>
     </row>
-    <row r="117" spans="1:17" s="5" customFormat="1">
+    <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>41365</v>
       </c>
@@ -7371,7 +7378,7 @@
         <v>-11.2</v>
       </c>
     </row>
-    <row r="118" spans="1:17" s="5" customFormat="1">
+    <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>41334</v>
       </c>
@@ -7424,7 +7431,7 @@
         <v>-14.5</v>
       </c>
     </row>
-    <row r="119" spans="1:17" s="5" customFormat="1">
+    <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>41306</v>
       </c>
@@ -7477,7 +7484,7 @@
         <v>-10.199999999999999</v>
       </c>
     </row>
-    <row r="120" spans="1:17" s="5" customFormat="1">
+    <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>41275</v>
       </c>
@@ -7530,7 +7537,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="121" spans="1:17" s="5" customFormat="1">
+    <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>41244</v>
       </c>
@@ -7583,7 +7590,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="5" customFormat="1">
+    <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>41214</v>
       </c>
@@ -7636,7 +7643,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="123" spans="1:17" s="5" customFormat="1">
+    <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>41183</v>
       </c>
@@ -7689,7 +7696,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="124" spans="1:17" s="5" customFormat="1">
+    <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>41153</v>
       </c>
@@ -7742,7 +7749,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="125" spans="1:17" s="5" customFormat="1">
+    <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>41122</v>
       </c>
@@ -7795,7 +7802,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="126" spans="1:17" s="5" customFormat="1">
+    <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>41091</v>
       </c>
@@ -7848,7 +7855,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:17" s="5" customFormat="1">
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>41061</v>
       </c>
@@ -7901,7 +7908,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:17" s="5" customFormat="1">
+    <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>41030</v>
       </c>
@@ -7954,7 +7961,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="129" spans="1:17" s="5" customFormat="1">
+    <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>41000</v>
       </c>
@@ -8007,7 +8014,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:17" s="5" customFormat="1">
+    <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>40969</v>
       </c>
@@ -8060,7 +8067,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="131" spans="1:17" s="5" customFormat="1">
+    <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>40940</v>
       </c>
@@ -8113,7 +8120,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" spans="1:17" s="5" customFormat="1">
+    <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>40909</v>
       </c>
@@ -8166,7 +8173,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:17" s="5" customFormat="1">
+    <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
         <v>40878</v>
       </c>
@@ -8219,7 +8226,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="134" spans="1:17" s="5" customFormat="1">
+    <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>40848</v>
       </c>
@@ -8272,7 +8279,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:17" s="5" customFormat="1">
+    <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
         <v>40817</v>
       </c>
@@ -8325,7 +8332,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="136" spans="1:17" s="5" customFormat="1">
+    <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>40787</v>
       </c>
@@ -8378,7 +8385,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="137" spans="1:17" s="5" customFormat="1">
+    <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
         <v>40756</v>
       </c>
@@ -8431,7 +8438,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" spans="1:17" s="5" customFormat="1">
+    <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>40725</v>
       </c>
@@ -8484,7 +8491,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="1:17" s="5" customFormat="1">
+    <row r="139" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
         <v>40695</v>
       </c>
@@ -8537,7 +8544,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:17" s="5" customFormat="1">
+    <row r="140" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>40664</v>
       </c>
@@ -8590,7 +8597,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="141" spans="1:17" s="5" customFormat="1">
+    <row r="141" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
         <v>40634</v>
       </c>
@@ -8643,7 +8650,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="142" spans="1:17" s="5" customFormat="1">
+    <row r="142" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>40603</v>
       </c>
@@ -8696,7 +8703,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="143" spans="1:17" s="5" customFormat="1">
+    <row r="143" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>40575</v>
       </c>
@@ -8749,7 +8756,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:17" s="5" customFormat="1">
+    <row r="144" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>40544</v>
       </c>
@@ -8802,7 +8809,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:17" s="5" customFormat="1">
+    <row r="145" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
         <v>40513</v>
       </c>
@@ -8855,7 +8862,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="146" spans="1:17" s="5" customFormat="1">
+    <row r="146" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>40483</v>
       </c>
@@ -8908,7 +8915,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="147" spans="1:17" s="5" customFormat="1">
+    <row r="147" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
         <v>40452</v>
       </c>
@@ -8961,7 +8968,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:17" s="5" customFormat="1">
+    <row r="148" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
         <v>40422</v>
       </c>
@@ -9014,7 +9021,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:17" s="5" customFormat="1">
+    <row r="149" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
         <v>40391</v>
       </c>
@@ -9067,7 +9074,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:17" s="5" customFormat="1">
+    <row r="150" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
         <v>40360</v>
       </c>
@@ -9120,7 +9127,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:17" s="5" customFormat="1">
+    <row r="151" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
         <v>40330</v>
       </c>
@@ -9173,7 +9180,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:17" s="5" customFormat="1">
+    <row r="152" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
         <v>40299</v>
       </c>
@@ -9226,7 +9233,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:17" s="5" customFormat="1">
+    <row r="153" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
         <v>40269</v>
       </c>
@@ -9279,7 +9286,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="154" spans="1:17" s="5" customFormat="1">
+    <row r="154" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
         <v>40238</v>
       </c>
@@ -9332,7 +9339,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="155" spans="1:17" s="5" customFormat="1">
+    <row r="155" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
         <v>40210</v>
       </c>
@@ -9385,7 +9392,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="156" spans="1:17" s="5" customFormat="1">
+    <row r="156" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
         <v>40179</v>
       </c>
@@ -9438,7 +9445,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="157" spans="1:17" s="5" customFormat="1">
+    <row r="157" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
         <v>40148</v>
       </c>
@@ -9491,7 +9498,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="158" spans="1:17" s="5" customFormat="1">
+    <row r="158" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
         <v>40118</v>
       </c>
@@ -9544,7 +9551,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:17" s="5" customFormat="1">
+    <row r="159" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
         <v>40087</v>
       </c>
@@ -9597,7 +9604,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="160" spans="1:17" s="5" customFormat="1">
+    <row r="160" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
         <v>40057</v>
       </c>
@@ -9650,7 +9657,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="161" spans="1:17" s="5" customFormat="1">
+    <row r="161" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A161" s="6">
         <v>40026</v>
       </c>
@@ -9703,7 +9710,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="162" spans="1:17" s="5" customFormat="1">
+    <row r="162" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A162" s="6">
         <v>39995</v>
       </c>
@@ -9756,7 +9763,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="163" spans="1:17" s="5" customFormat="1">
+    <row r="163" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A163" s="6">
         <v>39965</v>
       </c>
@@ -9809,7 +9816,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="164" spans="1:17" s="5" customFormat="1">
+    <row r="164" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A164" s="6">
         <v>39934</v>
       </c>
@@ -9862,7 +9869,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="165" spans="1:17" s="5" customFormat="1">
+    <row r="165" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A165" s="6">
         <v>39904</v>
       </c>
@@ -9915,7 +9922,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="166" spans="1:17" s="5" customFormat="1">
+    <row r="166" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A166" s="6">
         <v>39873</v>
       </c>
@@ -9968,7 +9975,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="167" spans="1:17" s="5" customFormat="1">
+    <row r="167" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
         <v>39845</v>
       </c>
@@ -10021,7 +10028,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:17" s="5" customFormat="1">
+    <row r="168" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A168" s="6">
         <v>39814</v>
       </c>
@@ -10074,7 +10081,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:17" s="5" customFormat="1">
+    <row r="169" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A169" s="6">
         <v>39783</v>
       </c>
@@ -10127,7 +10134,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:17" s="5" customFormat="1">
+    <row r="170" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A170" s="6">
         <v>39753</v>
       </c>
@@ -10180,7 +10187,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="171" spans="1:17" s="5" customFormat="1">
+    <row r="171" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
         <v>39722</v>
       </c>
@@ -10233,7 +10240,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:17" s="5" customFormat="1">
+    <row r="172" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
         <v>39692</v>
       </c>
@@ -10286,7 +10293,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:17" s="5" customFormat="1">
+    <row r="173" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
         <v>39661</v>
       </c>
@@ -10339,7 +10346,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="174" spans="1:17" s="5" customFormat="1">
+    <row r="174" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A174" s="6">
         <v>39630</v>
       </c>
@@ -10392,7 +10399,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:17" s="5" customFormat="1">
+    <row r="175" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A175" s="6">
         <v>39600</v>
       </c>
@@ -10445,7 +10452,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="1:17" s="5" customFormat="1">
+    <row r="176" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
         <v>39569</v>
       </c>
@@ -10498,7 +10505,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="177" spans="1:17" s="5" customFormat="1">
+    <row r="177" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
         <v>39539</v>
       </c>
@@ -10551,7 +10558,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:17" s="5" customFormat="1">
+    <row r="178" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
         <v>39508</v>
       </c>
@@ -10604,7 +10611,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:17" s="5" customFormat="1">
+    <row r="179" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
         <v>39479</v>
       </c>
@@ -10657,7 +10664,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="1:17" s="5" customFormat="1">
+    <row r="180" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
         <v>39448</v>
       </c>
@@ -10710,7 +10717,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:17" s="5" customFormat="1">
+    <row r="181" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
         <v>39417</v>
       </c>
@@ -10763,7 +10770,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="182" spans="1:17" s="5" customFormat="1">
+    <row r="182" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
         <v>39387</v>
       </c>
@@ -10816,7 +10823,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="1:17" s="5" customFormat="1">
+    <row r="183" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A183" s="6">
         <v>39356</v>
       </c>
@@ -10869,7 +10876,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="184" spans="1:17" s="5" customFormat="1">
+    <row r="184" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A184" s="6">
         <v>39326</v>
       </c>
@@ -10922,7 +10929,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="185" spans="1:17" s="5" customFormat="1">
+    <row r="185" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A185" s="6">
         <v>39295</v>
       </c>
@@ -10975,7 +10982,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:17" s="5" customFormat="1">
+    <row r="186" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A186" s="6">
         <v>39264</v>
       </c>
@@ -11028,7 +11035,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="1:17" s="5" customFormat="1">
+    <row r="187" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A187" s="6">
         <v>39234</v>
       </c>
@@ -11081,7 +11088,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="188" spans="1:17" s="5" customFormat="1">
+    <row r="188" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A188" s="6">
         <v>39203</v>
       </c>
@@ -11134,7 +11141,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="189" spans="1:17" s="5" customFormat="1">
+    <row r="189" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A189" s="6">
         <v>39173</v>
       </c>
@@ -11187,7 +11194,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="190" spans="1:17" s="5" customFormat="1">
+    <row r="190" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A190" s="6">
         <v>39142</v>
       </c>
@@ -11240,7 +11247,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="191" spans="1:17" s="5" customFormat="1">
+    <row r="191" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A191" s="6">
         <v>39114</v>
       </c>
@@ -11293,7 +11300,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="192" spans="1:17" s="5" customFormat="1">
+    <row r="192" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A192" s="6">
         <v>39083</v>
       </c>
@@ -11346,7 +11353,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="193" spans="1:17" s="5" customFormat="1">
+    <row r="193" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A193" s="6">
         <v>39052</v>
       </c>
@@ -11399,7 +11406,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:17" s="5" customFormat="1">
+    <row r="194" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A194" s="6">
         <v>39022</v>
       </c>
@@ -11452,7 +11459,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="195" spans="1:17" s="5" customFormat="1">
+    <row r="195" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A195" s="6">
         <v>38991</v>
       </c>
@@ -11505,7 +11512,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="196" spans="1:17" s="5" customFormat="1">
+    <row r="196" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A196" s="6">
         <v>38961</v>
       </c>
@@ -11558,7 +11565,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="197" spans="1:17" s="5" customFormat="1">
+    <row r="197" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A197" s="6">
         <v>38930</v>
       </c>
@@ -11611,7 +11618,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="198" spans="1:17" s="5" customFormat="1">
+    <row r="198" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A198" s="6">
         <v>38899</v>
       </c>
@@ -11664,7 +11671,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="199" spans="1:17" s="5" customFormat="1">
+    <row r="199" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A199" s="6">
         <v>38869</v>
       </c>
@@ -11717,7 +11724,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="200" spans="1:17" s="5" customFormat="1">
+    <row r="200" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <v>38838</v>
       </c>
@@ -11770,7 +11777,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="201" spans="1:17" s="5" customFormat="1">
+    <row r="201" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A201" s="6">
         <v>38808</v>
       </c>
@@ -11823,7 +11830,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="202" spans="1:17" s="5" customFormat="1">
+    <row r="202" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A202" s="6">
         <v>38777</v>
       </c>
@@ -11876,7 +11883,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="203" spans="1:17" s="5" customFormat="1">
+    <row r="203" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A203" s="6">
         <v>38749</v>
       </c>
@@ -11929,7 +11936,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="204" spans="1:17" s="5" customFormat="1">
+    <row r="204" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A204" s="6">
         <v>38718</v>
       </c>
@@ -11982,7 +11989,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="205" spans="1:17" s="5" customFormat="1">
+    <row r="205" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A205" s="6">
         <v>38687</v>
       </c>
@@ -12035,7 +12042,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:17" s="5" customFormat="1">
+    <row r="206" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A206" s="6">
         <v>38657</v>
       </c>
@@ -12088,7 +12095,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:17" s="5" customFormat="1">
+    <row r="207" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A207" s="6">
         <v>38626</v>
       </c>
@@ -12141,7 +12148,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="208" spans="1:17" s="5" customFormat="1">
+    <row r="208" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A208" s="6">
         <v>38596</v>
       </c>
@@ -12194,7 +12201,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="209" spans="1:17" s="5" customFormat="1">
+    <row r="209" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A209" s="6">
         <v>38565</v>
       </c>
@@ -12247,7 +12254,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="210" spans="1:17" s="5" customFormat="1">
+    <row r="210" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A210" s="6">
         <v>38534</v>
       </c>
@@ -12300,7 +12307,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="211" spans="1:17" s="5" customFormat="1">
+    <row r="211" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A211" s="6">
         <v>38504</v>
       </c>
@@ -12353,7 +12360,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="212" spans="1:17" s="5" customFormat="1">
+    <row r="212" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A212" s="6">
         <v>38473</v>
       </c>
@@ -12406,7 +12413,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="213" spans="1:17" s="5" customFormat="1">
+    <row r="213" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A213" s="6">
         <v>38443</v>
       </c>
@@ -12459,7 +12466,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="214" spans="1:17" s="5" customFormat="1">
+    <row r="214" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A214" s="6">
         <v>38412</v>
       </c>
@@ -12512,7 +12519,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="215" spans="1:17" s="5" customFormat="1">
+    <row r="215" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A215" s="6">
         <v>38384</v>
       </c>
@@ -12565,7 +12572,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="216" spans="1:17" s="5" customFormat="1">
+    <row r="216" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A216" s="6">
         <v>38353</v>
       </c>
@@ -12618,7 +12625,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="217" spans="1:17" s="5" customFormat="1">
+    <row r="217" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A217" s="6">
         <v>38322</v>
       </c>
@@ -12671,7 +12678,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="218" spans="1:17" s="5" customFormat="1">
+    <row r="218" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A218" s="6">
         <v>38292</v>
       </c>
@@ -12724,7 +12731,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="219" spans="1:17" s="5" customFormat="1">
+    <row r="219" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A219" s="6">
         <v>38261</v>
       </c>
@@ -12777,7 +12784,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="220" spans="1:17" s="5" customFormat="1">
+    <row r="220" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A220" s="6">
         <v>38231</v>
       </c>
@@ -12830,7 +12837,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="221" spans="1:17" s="5" customFormat="1">
+    <row r="221" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A221" s="6">
         <v>38200</v>
       </c>
@@ -12883,7 +12890,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="222" spans="1:17" s="5" customFormat="1">
+    <row r="222" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A222" s="6">
         <v>38169</v>
       </c>
@@ -12936,7 +12943,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="223" spans="1:17" s="5" customFormat="1">
+    <row r="223" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A223" s="6">
         <v>38139</v>
       </c>
@@ -12989,7 +12996,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="224" spans="1:17" s="5" customFormat="1">
+    <row r="224" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A224" s="6">
         <v>38108</v>
       </c>
@@ -13042,7 +13049,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="225" spans="1:17" s="5" customFormat="1">
+    <row r="225" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A225" s="6">
         <v>38078</v>
       </c>
@@ -13095,7 +13102,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="226" spans="1:17" s="5" customFormat="1">
+    <row r="226" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A226" s="6">
         <v>38047</v>
       </c>
@@ -13148,7 +13155,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="227" spans="1:17" s="5" customFormat="1">
+    <row r="227" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A227" s="6">
         <v>38018</v>
       </c>
@@ -13201,7 +13208,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="228" spans="1:17" s="5" customFormat="1">
+    <row r="228" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A228" s="6">
         <v>37987</v>
       </c>
@@ -13254,7 +13261,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="229" spans="1:17" s="5" customFormat="1">
+    <row r="229" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A229" s="6">
         <v>37956</v>
       </c>
@@ -13307,7 +13314,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="230" spans="1:17" s="5" customFormat="1">
+    <row r="230" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A230" s="6">
         <v>37926</v>
       </c>
@@ -13360,7 +13367,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="231" spans="1:17" s="5" customFormat="1">
+    <row r="231" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A231" s="6">
         <v>37895</v>
       </c>
@@ -13413,7 +13420,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="232" spans="1:17" s="5" customFormat="1">
+    <row r="232" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A232" s="6">
         <v>37865</v>
       </c>
@@ -13466,7 +13473,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="233" spans="1:17" s="5" customFormat="1">
+    <row r="233" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A233" s="6">
         <v>37834</v>
       </c>
@@ -13519,7 +13526,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="234" spans="1:17" s="5" customFormat="1">
+    <row r="234" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A234" s="6">
         <v>37803</v>
       </c>
@@ -13572,7 +13579,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="235" spans="1:17" s="5" customFormat="1">
+    <row r="235" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A235" s="6">
         <v>37773</v>
       </c>
@@ -13625,7 +13632,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="1:17" s="5" customFormat="1">
+    <row r="236" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A236" s="6">
         <v>37742</v>
       </c>
@@ -13678,7 +13685,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="237" spans="1:17" s="5" customFormat="1">
+    <row r="237" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A237" s="6">
         <v>37712</v>
       </c>
@@ -13731,7 +13738,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="238" spans="1:17" s="5" customFormat="1">
+    <row r="238" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A238" s="6">
         <v>37681</v>
       </c>
@@ -13784,7 +13791,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="239" spans="1:17" s="5" customFormat="1">
+    <row r="239" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A239" s="6">
         <v>37653</v>
       </c>
@@ -13837,7 +13844,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="1:17" s="5" customFormat="1">
+    <row r="240" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A240" s="6">
         <v>37622</v>
       </c>
@@ -13890,7 +13897,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="241" spans="1:17" s="5" customFormat="1">
+    <row r="241" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A241" s="6">
         <v>37591</v>
       </c>
@@ -13943,7 +13950,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="242" spans="1:17" s="5" customFormat="1">
+    <row r="242" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A242" s="6">
         <v>37561</v>
       </c>
@@ -13996,7 +14003,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="243" spans="1:17" s="5" customFormat="1">
+    <row r="243" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A243" s="6">
         <v>37530</v>
       </c>
@@ -14049,7 +14056,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="244" spans="1:17" s="5" customFormat="1">
+    <row r="244" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A244" s="6">
         <v>37500</v>
       </c>
@@ -14102,7 +14109,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="245" spans="1:17" s="5" customFormat="1">
+    <row r="245" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A245" s="6">
         <v>37469</v>
       </c>
@@ -14155,7 +14162,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="246" spans="1:17" s="5" customFormat="1">
+    <row r="246" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A246" s="6">
         <v>37438</v>
       </c>
@@ -14208,7 +14215,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="247" spans="1:17" s="5" customFormat="1">
+    <row r="247" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A247" s="6">
         <v>37408</v>
       </c>
@@ -14261,7 +14268,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="248" spans="1:17" s="5" customFormat="1">
+    <row r="248" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A248" s="6">
         <v>37377</v>
       </c>
@@ -14314,7 +14321,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="249" spans="1:17" s="5" customFormat="1">
+    <row r="249" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A249" s="6">
         <v>37347</v>
       </c>
@@ -14367,7 +14374,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="250" spans="1:17" s="5" customFormat="1">
+    <row r="250" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A250" s="6">
         <v>37316</v>
       </c>
@@ -14420,7 +14427,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="251" spans="1:17" s="5" customFormat="1">
+    <row r="251" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A251" s="6">
         <v>37288</v>
       </c>
@@ -14473,7 +14480,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="252" spans="1:17" s="5" customFormat="1">
+    <row r="252" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A252" s="6">
         <v>37257</v>
       </c>
@@ -14526,7 +14533,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="253" spans="1:17" s="5" customFormat="1">
+    <row r="253" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A253" s="6">
         <v>37226</v>
       </c>
@@ -14579,7 +14586,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="254" spans="1:17" s="5" customFormat="1">
+    <row r="254" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A254" s="6">
         <v>37196</v>
       </c>
@@ -14632,7 +14639,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="255" spans="1:17" s="5" customFormat="1">
+    <row r="255" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A255" s="6">
         <v>37165</v>
       </c>
@@ -14685,7 +14692,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="256" spans="1:17" s="5" customFormat="1">
+    <row r="256" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A256" s="6">
         <v>37135</v>
       </c>
@@ -14738,7 +14745,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="257" spans="1:17" s="5" customFormat="1">
+    <row r="257" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A257" s="6">
         <v>37104</v>
       </c>
@@ -14791,7 +14798,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="258" spans="1:17" s="5" customFormat="1">
+    <row r="258" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A258" s="6">
         <v>37073</v>
       </c>
@@ -14844,7 +14851,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="259" spans="1:17" s="5" customFormat="1">
+    <row r="259" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A259" s="6">
         <v>37043</v>
       </c>
@@ -14897,7 +14904,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="260" spans="1:17" s="5" customFormat="1">
+    <row r="260" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A260" s="6">
         <v>37012</v>
       </c>
@@ -14950,7 +14957,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="261" spans="1:17" s="5" customFormat="1">
+    <row r="261" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A261" s="6">
         <v>36982</v>
       </c>
@@ -15003,7 +15010,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="262" spans="1:17" s="5" customFormat="1">
+    <row r="262" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A262" s="6">
         <v>36951</v>
       </c>
@@ -15056,7 +15063,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="263" spans="1:17" s="5" customFormat="1">
+    <row r="263" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A263" s="6">
         <v>36923</v>
       </c>
@@ -15109,7 +15116,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="264" spans="1:17" s="5" customFormat="1">
+    <row r="264" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A264" s="6">
         <v>36892</v>
       </c>
@@ -15162,7 +15169,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="265" spans="1:17" s="5" customFormat="1">
+    <row r="265" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A265" s="6">
         <v>36861</v>
       </c>
@@ -15215,7 +15222,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="266" spans="1:17" s="5" customFormat="1">
+    <row r="266" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A266" s="6">
         <v>36831</v>
       </c>
@@ -15268,7 +15275,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="267" spans="1:17" s="5" customFormat="1">
+    <row r="267" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A267" s="6">
         <v>36800</v>
       </c>
@@ -15321,7 +15328,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="268" spans="1:17" s="5" customFormat="1">
+    <row r="268" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A268" s="6">
         <v>36770</v>
       </c>
@@ -15374,7 +15381,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="269" spans="1:17" s="5" customFormat="1">
+    <row r="269" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A269" s="6">
         <v>36739</v>
       </c>
@@ -15427,7 +15434,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="270" spans="1:17" s="5" customFormat="1">
+    <row r="270" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A270" s="6">
         <v>36708</v>
       </c>
@@ -15480,7 +15487,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="271" spans="1:17" s="5" customFormat="1">
+    <row r="271" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A271" s="6">
         <v>36678</v>
       </c>
@@ -15533,7 +15540,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="272" spans="1:17" s="5" customFormat="1">
+    <row r="272" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A272" s="6">
         <v>36647</v>
       </c>
@@ -15586,7 +15593,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="273" spans="1:17" s="5" customFormat="1">
+    <row r="273" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A273" s="6">
         <v>36617</v>
       </c>
@@ -15639,7 +15646,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="274" spans="1:17" s="5" customFormat="1">
+    <row r="274" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A274" s="6">
         <v>36586</v>
       </c>
@@ -15692,7 +15699,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="275" spans="1:17" s="5" customFormat="1">
+    <row r="275" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A275" s="6">
         <v>36557</v>
       </c>
@@ -15745,7 +15752,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="276" spans="1:17" s="5" customFormat="1">
+    <row r="276" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A276" s="6">
         <v>36526</v>
       </c>
@@ -15798,7 +15805,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="277" spans="1:17" s="5" customFormat="1">
+    <row r="277" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A277" s="6">
         <v>36495</v>
       </c>
@@ -15851,7 +15858,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="278" spans="1:17" s="5" customFormat="1">
+    <row r="278" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A278" s="6">
         <v>36465</v>
       </c>
@@ -15904,7 +15911,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="279" spans="1:17" s="5" customFormat="1">
+    <row r="279" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A279" s="6">
         <v>36434</v>
       </c>
@@ -15957,7 +15964,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="280" spans="1:17" s="5" customFormat="1">
+    <row r="280" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A280" s="6">
         <v>36404</v>
       </c>
@@ -16010,7 +16017,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="281" spans="1:17" s="5" customFormat="1">
+    <row r="281" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A281" s="6">
         <v>36373</v>
       </c>
@@ -16063,7 +16070,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="282" spans="1:17" s="5" customFormat="1">
+    <row r="282" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A282" s="6">
         <v>36342</v>
       </c>
@@ -16116,7 +16123,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="283" spans="1:17" s="5" customFormat="1">
+    <row r="283" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A283" s="6">
         <v>36312</v>
       </c>
@@ -16169,7 +16176,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="284" spans="1:17" s="5" customFormat="1">
+    <row r="284" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A284" s="6">
         <v>36281</v>
       </c>
@@ -16222,7 +16229,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="285" spans="1:17" s="5" customFormat="1">
+    <row r="285" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A285" s="6">
         <v>36251</v>
       </c>
@@ -16275,7 +16282,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="286" spans="1:17" s="5" customFormat="1">
+    <row r="286" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A286" s="6">
         <v>36220</v>
       </c>
@@ -16328,7 +16335,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="287" spans="1:17" s="5" customFormat="1">
+    <row r="287" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A287" s="6">
         <v>36192</v>
       </c>
@@ -16381,7 +16388,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="288" spans="1:17" s="5" customFormat="1">
+    <row r="288" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A288" s="6">
         <v>36161</v>
       </c>
@@ -16449,7 +16456,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>